--- a/Configs/GameConfig/Datas/DropConfig.xlsx
+++ b/Configs/GameConfig/Datas/DropConfig.xlsx
@@ -479,9 +479,6 @@
       <c r="O1" t="str">
         <v>GroundGravity</v>
       </c>
-      <c r="P1" t="str">
-        <v>GroundPickupRadius</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -491,7 +488,6 @@
       </c>
       <c r="N2"/>
       <c r="O2"/>
-      <c r="P2"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -565,9 +561,6 @@
       <c r="O3" t="str">
         <v>float</v>
       </c>
-      <c r="P3" t="str">
-        <v>float</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -577,7 +570,6 @@
       </c>
       <c r="N4"/>
       <c r="O4"/>
-      <c r="P4"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -649,9 +641,6 @@
       <c r="O5" t="str">
         <v>地面掉落重力 px/s²</v>
       </c>
-      <c r="P5" t="str">
-        <v>拾取范围扩展 px</v>
-      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -699,9 +688,6 @@
       </c>
       <c r="O6" t="n">
         <v>980</v>
-      </c>
-      <c r="P6" t="n">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
